--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -523,10 +523,96 @@
       <c r="C11" t="str">
         <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>4</v>
+      </c>
+      <c r="C12" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>169_欢乐颂_Silantoi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>5</v>
+      </c>
+      <c r="C18" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>705_中华桔梗紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010106138148130</v>
+        <v>0201010613814813101072868202050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -609,10 +609,104 @@
       <c r="A21" t="str">
         <v>6</v>
       </c>
+      <c r="C21" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>570_水蜡烛_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2</v>
+      </c>
+      <c r="C26" t="str">
+        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>3</v>
+      </c>
+      <c r="C27" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,7 +761,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010613814813101072868202050</v>
+        <v>0201010613814813101072868202053105520201029550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -703,6 +703,9 @@
         <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
 red /green /orange / yellow_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -761,7 +764,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010613814813101072868202053105520201029550</v>
+        <v>0201010613814813101072868202053105520201029554</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -707,9 +707,93 @@
         <v>4</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>4</v>
+      </c>
+      <c r="C32" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">345_天竺少女_Cryptomeria
+Kashiwaba_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>5</v>
+      </c>
+      <c r="C40" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -764,7 +848,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010613814813101072868202053105520201029554</v>
+        <v>020101061381481310107286820205310552020102955415792261330</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -790,6 +790,9 @@
       <c r="C41" t="str">
         <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -848,7 +851,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101061381481310107286820205310552020102955415792261330</v>
+        <v>0201010613814813101072868202053105520201029554157922613318</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -783,20 +783,98 @@
         <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F40" t="str">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F41" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">345_天竺少女_Cryptomeria
+Kashiwaba_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>6</v>
+      </c>
+      <c r="C44" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
         <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F45" t="str">
         <v>18</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>261_单头蓝莓_Blueberry_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>7</v>
+      </c>
+      <c r="C49" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">345_天竺少女_Cryptomeria
+Kashiwaba_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -851,7 +929,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010613814813101072868202053105520201029554157922613318</v>
+        <v>020101061381481310107286820205310552020102955415792261317148231810118100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -871,6 +871,9 @@
         <v xml:space="preserve">345_天竺少女_Cryptomeria
 Kashiwaba_undefined_1bunch</v>
       </c>
+      <c r="F50" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -929,7 +932,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101061381481310107286820205310552020102955415792261317148231810118100</v>
+        <v>020101061381481310107286820205310552020102955415792261317148231810118105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -875,9 +875,25 @@
         <v>5</v>
       </c>
     </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L52"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -932,7 +948,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101061381481310107286820205310552020102955415792261317148231810118105</v>
+        <v>020101061381481310107286820205310552020102955415792261317148231810118105203</v>
       </c>
     </row>
   </sheetData>
